--- a/utils/monday_sprint_sprint_2024-29.xlsx
+++ b/utils/monday_sprint_sprint_2024-29.xlsx
@@ -132,7 +132,7 @@
     <t>17/03/2023</t>
   </si>
   <si>
-    <t>09/05/2026</t>
+    <t>04/05/2026</t>
   </si>
   <si>
     <t>Março</t>
@@ -2712,7 +2712,7 @@
         <v>21</v>
       </c>
       <c r="Q10">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -2744,7 +2744,7 @@
         <v>92</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -2858,7 +2858,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>34</v>

--- a/utils/monday_sprint_sprint_2024-29.xlsx
+++ b/utils/monday_sprint_sprint_2024-29.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="159">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -87,7 +87,7 @@
     <t>05/02/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>18/02/2024</t>
   </si>
   <si>
     <t>Feito</t>
@@ -108,7 +108,7 @@
     <t>6002115297</t>
   </si>
   <si>
-    <t>24147</t>
+    <t>5893269209</t>
   </si>
   <si>
     <t>Melhoria</t>
@@ -129,12 +129,15 @@
     <t>Janeiro</t>
   </si>
   <si>
-    <t>22994</t>
+    <t>6003919725</t>
   </si>
   <si>
     <t>Dados mestres</t>
   </si>
   <si>
+    <t>6003969029</t>
+  </si>
+  <si>
     <t>Apontamentos</t>
   </si>
   <si>
@@ -162,28 +165,49 @@
     <t>04/05/2026</t>
   </si>
   <si>
-    <t>24260</t>
+    <t>6003804898</t>
   </si>
   <si>
     <t>Movimentação retroativa - Criar campos na estrutura de registros de End n° Linha e Processo Aprovado S/N</t>
   </si>
   <si>
+    <t>12/02/2024</t>
+  </si>
+  <si>
+    <t>6003814746</t>
+  </si>
+  <si>
     <t>Movimentação retroativa - Ajustar parâmetros</t>
   </si>
   <si>
+    <t>14/02/2024</t>
+  </si>
+  <si>
+    <t>6003822713</t>
+  </si>
+  <si>
     <t>Movimentação retroativa - Montar Tela de chamada da movimentação retroativa</t>
   </si>
   <si>
+    <t>6003823172</t>
+  </si>
+  <si>
     <t>Movimentação retroativa - Fazer Consistência</t>
   </si>
   <si>
+    <t>6003823504</t>
+  </si>
+  <si>
     <t>Movimentação retroativa - Movimentação por peça com registro concluído</t>
   </si>
   <si>
+    <t>6003823799</t>
+  </si>
+  <si>
     <t>Movimentação retroativa - Alterar telas de consulta que o registro de End está concluído</t>
   </si>
   <si>
-    <t>24443</t>
+    <t>6009036025</t>
   </si>
   <si>
     <t>Dashboard desmoldagem</t>
@@ -192,7 +216,10 @@
     <t>06/02/2024</t>
   </si>
   <si>
-    <t>7935</t>
+    <t>17/02/2024</t>
+  </si>
+  <si>
+    <t>1407234802</t>
   </si>
   <si>
     <t>Novo Recurso</t>
@@ -207,10 +234,13 @@
     <t>20/06/2021</t>
   </si>
   <si>
+    <t>08/02/2024</t>
+  </si>
+  <si>
     <t>Junho</t>
   </si>
   <si>
-    <t>15593</t>
+    <t>3262290129</t>
   </si>
   <si>
     <t>Informar se a sequência é de amostra no relatório de etiqueta amarela</t>
@@ -222,7 +252,7 @@
     <t>Setembro</t>
   </si>
   <si>
-    <t>24307</t>
+    <t>5990271651</t>
   </si>
   <si>
     <t>Inserir Coluna "Tem Retorno para Usinagem?"</t>
@@ -231,61 +261,70 @@
     <t>02/02/2024</t>
   </si>
   <si>
-    <t>24295</t>
+    <t>5990467520</t>
   </si>
   <si>
     <t>Cadastro de item - Compra spot</t>
   </si>
   <si>
-    <t>24289</t>
+    <t>5990481755</t>
   </si>
   <si>
     <t>Melhorias e Alterações - Controle na moldagem + planilhão</t>
   </si>
   <si>
-    <t>24282</t>
+    <t>5990505318</t>
   </si>
   <si>
     <t>Melhoria sistema de corridas</t>
   </si>
   <si>
-    <t>24395</t>
+    <t>15/02/2024</t>
+  </si>
+  <si>
+    <t>5989828553</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Integração Contábil Imobilizado</t>
   </si>
   <si>
-    <t>24250</t>
+    <t>5990606317</t>
   </si>
   <si>
     <t>WMS - Plano de ação</t>
   </si>
   <si>
-    <t>24389</t>
+    <t>11/02/2024</t>
+  </si>
+  <si>
+    <t>5989862737</t>
   </si>
   <si>
     <t>SISTEMA CARREGAMENTO EXPEDIÇÃO</t>
   </si>
   <si>
-    <t>24223</t>
+    <t>5990614127</t>
   </si>
   <si>
     <t>Relatório de programação de moldagem</t>
   </si>
   <si>
-    <t>24328</t>
+    <t>5990719114</t>
   </si>
   <si>
     <t>Divergência na comparação de notas com os romaneios</t>
   </si>
   <si>
-    <t>24342</t>
+    <t>13/02/2024</t>
+  </si>
+  <si>
+    <t>5989992771</t>
   </si>
   <si>
     <t>Valor do estoque</t>
   </si>
   <si>
-    <t>24418</t>
+    <t>5998594944</t>
   </si>
   <si>
     <t>Relatório Urgente Pauta diretoria</t>
@@ -294,13 +333,13 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>24341</t>
+    <t>5990038826</t>
   </si>
   <si>
     <t>Sense 22</t>
   </si>
   <si>
-    <t>24405</t>
+    <t>5999483006</t>
   </si>
   <si>
     <t>Correção</t>
@@ -309,37 +348,34 @@
     <t>Apontamento de Paradas Rebarbação "APON31"</t>
   </si>
   <si>
-    <t>24337</t>
+    <t>5990052695</t>
   </si>
   <si>
     <t>Trava para lançamento CTes</t>
   </si>
   <si>
-    <t>24308</t>
+    <t>5990125176</t>
   </si>
   <si>
     <t>Inserir Coluna "Tem Etapa da Prensa?"</t>
   </si>
   <si>
-    <t>24355</t>
+    <t>5989926693</t>
   </si>
   <si>
     <t>Sistema de saída expedição</t>
   </si>
   <si>
-    <t>18631</t>
+    <t>6029916622</t>
   </si>
   <si>
     <t>Novo relatório - Relatório de Custos por Nota Fiscal</t>
   </si>
   <si>
-    <t>08/02/2024</t>
-  </si>
-  <si>
     <t>Semana 2</t>
   </si>
   <si>
-    <t>24511</t>
+    <t>6036618281</t>
   </si>
   <si>
     <t>Crédito de PIS e COFINS nas devoluções</t>
@@ -348,22 +384,19 @@
     <t>09/02/2024</t>
   </si>
   <si>
-    <t>24579</t>
+    <t>6070121372</t>
   </si>
   <si>
     <t>Fluxo de Produção - Ajuste</t>
   </si>
   <si>
-    <t>15/02/2024</t>
-  </si>
-  <si>
-    <t>24387</t>
+    <t>5989880496</t>
   </si>
   <si>
     <t>PERGUNTAS BALANCEAMENTO PARA CONFIRMAÇÃO TÉCNICA</t>
   </si>
   <si>
-    <t>24357</t>
+    <t>5989901155</t>
   </si>
   <si>
     <t>Tempo de alguns setores do Pré-produtivo</t>
@@ -375,7 +408,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-29</t>
+    <t>Jun/2021</t>
   </si>
   <si>
     <t>Base</t>
@@ -1175,7 +1208,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1187,10 +1220,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
@@ -1222,37 +1255,37 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1269,7 +1302,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1281,10 +1314,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>34</v>
@@ -1299,7 +1332,7 @@
         <v>23</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1316,7 +1349,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1328,10 +1361,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
@@ -1346,7 +1379,7 @@
         <v>23</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1363,7 +1396,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1375,10 +1408,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>34</v>
@@ -1410,7 +1443,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1422,10 +1455,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>34</v>
@@ -1457,7 +1490,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1469,10 +1502,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>34</v>
@@ -1504,7 +1537,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1516,10 +1549,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>34</v>
@@ -1551,7 +1584,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1563,10 +1596,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>34</v>
@@ -1578,10 +1611,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1598,25 +1631,25 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>21</v>
@@ -1625,10 +1658,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1640,27 +1673,27 @@
         <v>36</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>34</v>
@@ -1672,10 +1705,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1687,12 +1720,12 @@
         <v>36</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1704,10 +1737,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>34</v>
@@ -1719,10 +1752,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1739,7 +1772,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1751,10 +1784,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>34</v>
@@ -1766,10 +1799,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1786,7 +1819,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1798,10 +1831,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>34</v>
@@ -1813,10 +1846,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1833,7 +1866,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1845,10 +1878,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>34</v>
@@ -1860,10 +1893,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1880,7 +1913,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1892,10 +1925,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>34</v>
@@ -1907,10 +1940,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1927,7 +1960,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1939,10 +1972,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>34</v>
@@ -1954,10 +1987,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1974,7 +2007,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -1986,10 +2019,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>34</v>
@@ -2001,10 +2034,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2021,7 +2054,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2033,10 +2066,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>34</v>
@@ -2048,10 +2081,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2068,7 +2101,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2080,10 +2113,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>34</v>
@@ -2095,10 +2128,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2115,7 +2148,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2127,10 +2160,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>34</v>
@@ -2142,10 +2175,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2162,7 +2195,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2174,13 +2207,13 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>21</v>
@@ -2192,7 +2225,7 @@
         <v>23</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2209,7 +2242,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2221,10 +2254,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>34</v>
@@ -2236,10 +2269,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2256,22 +2289,22 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>34</v>
@@ -2286,7 +2319,7 @@
         <v>23</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2303,7 +2336,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2315,10 +2348,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>34</v>
@@ -2330,10 +2363,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2350,7 +2383,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2362,10 +2395,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>34</v>
@@ -2377,10 +2410,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2397,7 +2430,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2409,10 +2442,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>34</v>
@@ -2424,10 +2457,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2444,7 +2477,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2456,10 +2489,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>34</v>
@@ -2471,10 +2504,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2483,7 +2516,7 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>28</v>
@@ -2491,7 +2524,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2503,10 +2536,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>34</v>
@@ -2518,10 +2551,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2530,7 +2563,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>28</v>
@@ -2538,7 +2571,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2550,10 +2583,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>34</v>
@@ -2565,10 +2598,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2585,7 +2618,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2597,10 +2630,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>34</v>
@@ -2612,7 +2645,7 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>24</v>
@@ -2632,7 +2665,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2644,10 +2677,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>34</v>
@@ -2659,7 +2692,7 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>24</v>
@@ -2690,23 +2723,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B2" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2714,16 +2747,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2734,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>820</v>
+        <v>72.51</v>
       </c>
       <c r="J5" s="4">
         <v>2</v>
@@ -2742,7 +2775,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2755,7 +2788,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2763,7 +2796,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2794,12 +2827,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B2">
         <v>37</v>
@@ -2813,7 +2846,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>820</v>
+        <v>72.51</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2823,25 +2856,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2858,13 +2891,13 @@
         <v>31</v>
       </c>
       <c r="G10" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2879,12 +2912,12 @@
         <v>27</v>
       </c>
       <c r="Q10">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -2896,7 +2929,7 @@
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -2908,21 +2941,21 @@
         <v>37</v>
       </c>
       <c r="M11" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -2934,13 +2967,13 @@
         <v>32</v>
       </c>
       <c r="J12" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -2949,24 +2982,24 @@
         <v>36</v>
       </c>
       <c r="Q12">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2980,7 +3013,7 @@
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2988,7 +3021,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2996,7 +3029,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3004,7 +3037,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3012,10 +3045,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3023,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3031,16 +3064,16 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F21" s="2">
-        <v>805</v>
+        <v>1766</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3051,7 +3084,7 @@
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>19</v>
@@ -3065,7 +3098,7 @@
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>19</v>
@@ -3079,7 +3112,7 @@
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>19</v>
@@ -3093,7 +3126,7 @@
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>33</v>
@@ -3107,7 +3140,7 @@
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>39</v>
@@ -3115,58 +3148,58 @@
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
